--- a/backtest_runs/20260410_193731/by_symbol/ORM/ORM.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/ORM/ORM.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>101669.91</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>101669.91</v>
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>109233.62</v>
@@ -955,7 +955,7 @@
         <v>-4125.659999999999</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>105992.03</v>
@@ -1047,7 +1047,7 @@
         <v>-884.0699999999986</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>107760.17</v>
@@ -1139,7 +1139,7 @@
         <v>-1866.369999999995</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>105893.8</v>
@@ -1185,7 +1185,7 @@
         <v>-982.3000000000139</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>104911.5</v>
@@ -1415,7 +1415,7 @@
         <v>-3143.360000000003</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>105992.03</v>
@@ -1553,7 +1553,7 @@
         <v>-2455.75</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>106483.18</v>
